--- a/periferia_v2/data/Generales_para_todos.xlsx
+++ b/periferia_v2/data/Generales_para_todos.xlsx
@@ -2528,20 +2528,20 @@
   </sheetData>
   <autoFilter ref="A1:B113"/>
   <mergeCells count="14">
-    <mergeCell ref="A63:A76"/>
     <mergeCell ref="A114:A122"/>
     <mergeCell ref="A26:A38"/>
     <mergeCell ref="A123:A134"/>
     <mergeCell ref="A39:A49"/>
     <mergeCell ref="A50:A62"/>
     <mergeCell ref="A15:A25"/>
+    <mergeCell ref="A146:A159"/>
     <mergeCell ref="A91:A98"/>
     <mergeCell ref="A99:A113"/>
     <mergeCell ref="A77:A90"/>
     <mergeCell ref="A135:A145"/>
     <mergeCell ref="A2:A14"/>
     <mergeCell ref="A160:A167"/>
-    <mergeCell ref="A146:A159"/>
+    <mergeCell ref="A63:A76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2604,9 +2604,7 @@
       <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Experto en desarrollo de servicios backend robustos y escalables usando Java.
-Implementa APIs REST, lógica de negocio y arquitectura basada en microservicios.
-Maneja frameworks como Spring Boot, Hibernate y JPA.
-Garantiza seguridad, rendimiento y buenas prácticas de codificación.</t>
+Implementa APIs REST, lógica de negocio y arquitectura basada en microservicios.</t>
         </is>
       </c>
     </row>
@@ -2621,9 +2619,7 @@
       <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Experto en desarrollo backend utilizando Node.js y arquitecturas orientadas a servicios.
-Construye APIs REST y GraphQL con Express o frameworks modernos.
-Gestiona integraciones, autenticación y procesamiento asíncrono.
-Optimiza rendimiento y escalabilidad en entornos cloud.</t>
+Construye APIs REST y GraphQL con Express o frameworks modernos.</t>
         </is>
       </c>
     </row>
@@ -2638,9 +2634,7 @@
       <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Experto en desarrollo backend con tecnologías .NET y C#.
-Implementa servicios REST, lógica empresarial y control de acceso.
-Trabaja con ASP.NET Core, Entity Framework y bases de datos relacionales.
-Asegura aplicaciones seguras, mantenibles y de alto rendimiento.</t>
+Implementa servicios REST, lógica empresarial y control de acceso.</t>
         </is>
       </c>
     </row>
@@ -2656,8 +2650,7 @@
         <is>
           <t>Experto en desarrollo backend utilizando Python para soluciones escalables.
 Implementa APIs con frameworks como Django y FastAPI.
-Integra servicios, bases de datos y procesos automatizados.
-Aplica buenas prácticas de seguridad y rendimiento.</t>
+Integra servicios, bases de datos y procesos automatizados.</t>
         </is>
       </c>
     </row>
@@ -2672,9 +2665,7 @@
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Experto en desarrollo backend con PHP para aplicaciones web.
-Construye APIs y lógica de negocio con frameworks como Laravel o Symfony.
-Gestiona integraciones con bases de datos y servicios externos.
-Garantiza estabilidad, seguridad y mantenibilidad del código.</t>
+Construye APIs y lógica de negocio con frameworks como Laravel o Symfony.</t>
         </is>
       </c>
     </row>
@@ -2690,8 +2681,7 @@
         <is>
           <t>Experto en desarrollo backend de alto rendimiento con Go.
 Diseña servicios eficientes y concurrentes orientados a microservicios.
-Implementa APIs REST y sistemas distribuidos.
-Optimiza consumo de recursos y tiempos de respuesta.</t>
+Implementa APIs REST y sistemas distribuidos.</t>
         </is>
       </c>
     </row>
@@ -2707,8 +2697,7 @@
         <is>
           <t>Experto en desarrollo de interfaces web con Angular.
 Construye aplicaciones escalables basadas en componentes.
-Implementa consumo de APIs, validaciones y manejo de estados.
-Garantiza buenas prácticas de usabilidad y rendimiento.</t>
+Implementa consumo de APIs, validaciones y manejo de estados.</t>
         </is>
       </c>
     </row>
@@ -2724,8 +2713,7 @@
         <is>
           <t>Experto en desarrollo frontend usando React y ecosistema moderno.
 Crea interfaces dinámicas basadas en componentes reutilizables.
-Gestiona estados con Redux o herramientas similares.
-Optimiza experiencia de usuario y rendimiento visual.</t>
+Gestiona estados con Redux o herramientas similares.</t>
         </is>
       </c>
     </row>
@@ -2758,8 +2746,7 @@
         <is>
           <t>Experto en diseño y desarrollo de experiencias de usuario.
 Aplica principios de usabilidad, accesibilidad y diseño visual.
-Colabora con equipos técnicos para una correcta implementación.
-Optimiza la interacción entre el usuario y la aplicación.</t>
+Colabora con equipos técnicos para una correcta implementación.</t>
         </is>
       </c>
     </row>
@@ -2775,8 +2762,7 @@
         <is>
           <t>Experto en desarrollo frontend y backend con tecnologías Java.
 Construye soluciones completas desde la interfaz hasta la base de datos.
-Integra servicios, APIs y lógica de negocio.
-Garantiza calidad, seguridad y escalabilidad del sistema.</t>
+Integra servicios, APIs y lógica de negocio.</t>
         </is>
       </c>
     </row>
@@ -2792,8 +2778,7 @@
         <is>
           <t>Experto en desarrollo integral con Node.js y tecnologías web modernas.
 Implementa frontend, backend e integraciones.
-Diseña soluciones orientadas a servicios y microservicios.
-Optimiza rendimiento y experiencia de usuario.</t>
+Diseña soluciones orientadas a servicios y microservicios.</t>
         </is>
       </c>
     </row>
@@ -2877,8 +2862,7 @@
         <is>
           <t>Experto en soluciones completas usando Angular y backend asociado.
 Desarrolla interfaces modernas y servicios integrados.
-Gestiona comunicación con APIs y bases de datos.
-Garantiza aplicaciones escalables y mantenibles.</t>
+Gestiona comunicación con APIs y bases de datos.</t>
         </is>
       </c>
     </row>
@@ -2894,8 +2878,7 @@
         <is>
           <t>Experto en desarrollo frontend con React y backend integrado.
 Construye soluciones completas y modernas.
-Gestiona estados, servicios y persistencia de datos.
-Optimiza experiencia de usuario y rendimiento.</t>
+Gestiona estados, servicios y persistencia de datos.</t>
         </is>
       </c>
     </row>
@@ -2936,8 +2919,7 @@
         <is>
           <t>Experto en validación funcional de aplicaciones y sistemas.
 Diseña y ejecuta casos de prueba basados en requerimientos.
-Identifica defectos en flujos de negocio.
-Garantiza que el sistema cumpla con lo esperado por el usuario.</t>
+Identifica defectos en flujos de negocio.</t>
         </is>
       </c>
     </row>
@@ -2953,8 +2935,7 @@
         <is>
           <t>Experto en pruebas de rendimiento, seguridad y usabilidad.
 Evalúa estabilidad, carga y comportamiento del sistema.
-Identifica riesgos técnicos y de desempeño.
-Asegura la calidad integral de la solución.</t>
+Identifica riesgos técnicos y de desempeño.</t>
         </is>
       </c>
     </row>
@@ -2970,8 +2951,7 @@
         <is>
           <t>Experto en liderazgo y coordinación de equipos de QA.
 Define estrategias, planes y estándares de calidad.
-Supervisa ejecución de pruebas funcionales y técnicas.
-Garantiza cumplimiento de objetivos de calidad.</t>
+Supervisa ejecución de pruebas funcionales y técnicas.</t>
         </is>
       </c>
     </row>
@@ -2987,8 +2967,7 @@
         <is>
           <t>Experto en automatización de pruebas funcionales y regresión.
 Diseña scripts con herramientas especializadas.
-Optimiza tiempos de prueba y detección temprana de fallos.
-Asegura estabilidad en entregas continuas.</t>
+Optimiza tiempos de prueba y detección temprana de fallos.</t>
         </is>
       </c>
     </row>
@@ -3012,8 +2991,7 @@
         <is>
           <t>Experto en diseño de arquitecturas de software empresariales.
 Define patrones, estándares y lineamientos técnicos.
-Garantiza escalabilidad, seguridad y mantenibilidad.
-Alinea la solución con los objetivos del negocio.</t>
+Garantiza escalabilidad, seguridad y mantenibilidad.</t>
         </is>
       </c>
     </row>
@@ -3087,9 +3065,7 @@
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Experto en diseño, construcción y mantenimiento de pipelines de datos.
-Gestiona ingesta, transformación y almacenamiento de grandes volúmenes.
-Trabaja con bases de datos, ETL y entornos cloud.
-Garantiza calidad, disponibilidad y eficiencia de los datos.</t>
+Gestiona ingesta, transformación y almacenamiento de grandes volúmenes.</t>
         </is>
       </c>
     </row>
@@ -3105,8 +3081,7 @@
         <is>
           <t>Experto en análisis, interpretación y visualización de datos.
 Transforma datos en información útil para la toma de decisiones.
-Utiliza herramientas de BI y análisis estadístico.
-Apoya la estrategia del negocio con insights claros.</t>
+Utiliza herramientas de BI y análisis estadístico.</t>
         </is>
       </c>
     </row>
@@ -3122,8 +3097,7 @@
         <is>
           <t>Experto en diseño de arquitecturas de datos empresariales.
 Define modelos, flujos y estándares de información.
-Garantiza integridad, seguridad y escalabilidad.
-Alinea la gestión de datos con objetivos del negocio.</t>
+Garantiza integridad, seguridad y escalabilidad.</t>
         </is>
       </c>
     </row>
@@ -3139,8 +3113,7 @@
         <is>
           <t>Experto en liderazgo técnico de equipos de datos.
 Define lineamientos, arquitecturas y buenas prácticas.
-Supervisa la implementación de soluciones analíticas.
-Asegura calidad técnica y cumplimiento de objetivos.</t>
+Supervisa la implementación de soluciones analíticas.</t>
         </is>
       </c>
     </row>
@@ -3156,8 +3129,7 @@
         <is>
           <t>Experto en análisis avanzado, estadística y modelos predictivos.
 Desarrolla algoritmos de machine learning y análisis exploratorio.
-Extrae patrones y predicciones a partir de datos.
-Apoya decisiones estratégicas basadas en datos.</t>
+Extrae patrones y predicciones a partir de datos.</t>
         </is>
       </c>
     </row>
@@ -3300,8 +3272,7 @@
         <is>
           <t>Experto en arquitectura y desarrollo avanzado en Dynamics CRM.
 Diseña soluciones empresariales complejas.
-Lidera integraciones y personalizaciones críticas.
-Asegura alineación con la estrategia del negocio.</t>
+Lidera integraciones y personalizaciones críticas.</t>
         </is>
       </c>
     </row>
@@ -3577,8 +3548,7 @@
         <is>
           <t>Experto en identificación y gestión de riesgos de seguridad.
 Evalúa vulnerabilidades y define controles de protección.
-Apoya implementación de políticas de seguridad.
-Garantiza integridad y confidencialidad de la información.</t>
+Apoya implementación de políticas de seguridad.</t>
         </is>
       </c>
     </row>
@@ -3594,8 +3564,7 @@
         <is>
           <t>Experto en análisis y mitigación de amenazas de ciberseguridad.
 Monitorea sistemas y detecta incidentes de seguridad.
-Implementa controles y buenas prácticas de seguridad.
-Apoya la protección de activos digitales.</t>
+Implementa controles y buenas prácticas de seguridad.</t>
         </is>
       </c>
     </row>
@@ -3644,8 +3613,7 @@
         <is>
           <t>Experto en gestión de materiales y cadena de suministro en SAP.
 Configura procesos de compras, inventarios y proveedores.
-Optimiza abastecimiento y control de stock.
-Alinea el módulo con las necesidades del negocio.</t>
+Optimiza abastecimiento y control de stock.</t>
         </is>
       </c>
     </row>
@@ -3661,8 +3629,7 @@
         <is>
           <t>Experto en gestión de ventas y distribución en SAP.
 Configura procesos de pedidos, facturación y entregas.
-Optimiza el ciclo comercial y la relación con clientes.
-Asegura correcta integración con otros módulos.</t>
+Optimiza el ciclo comercial y la relación con clientes.</t>
         </is>
       </c>
     </row>
@@ -3678,8 +3645,7 @@
         <is>
           <t>Experto en control de costos y contabilidad interna en SAP.
 Configura centros de costo, órdenes internas y análisis financiero.
-Apoya la planificación y control presupuestal.
-Optimiza la rentabilidad del negocio.</t>
+Apoya la planificación y control presupuestal.</t>
         </is>
       </c>
     </row>
@@ -3695,8 +3661,7 @@
         <is>
           <t>Experto en contabilidad financiera y gestión contable en SAP.
 Configura procesos de contabilidad general y fiscal.
-Asegura cumplimiento normativo y financiero.
-Optimiza el cierre contable y reportes financieros.</t>
+Asegura cumplimiento normativo y financiero.</t>
         </is>
       </c>
     </row>
@@ -3712,8 +3677,7 @@
         <is>
           <t>Experto en gestión de almacenes mediante SAP WM.
 Configura procesos de recepción, almacenamiento y despacho.
-Optimiza la logística interna y control de inventarios.
-Mejora la eficiencia operativa del almacén.</t>
+Optimiza la logística interna y control de inventarios.</t>
         </is>
       </c>
     </row>
@@ -3746,8 +3710,7 @@
         <is>
           <t>Experto en planificación y control de la producción en SAP.
 Configura órdenes de producción y listas de materiales.
-Optimiza la programación y capacidad productiva.
-Mejora la eficiencia de los procesos productivos.</t>
+Optimiza la programación y capacidad productiva.</t>
         </is>
       </c>
     </row>
@@ -3831,8 +3794,7 @@
         <is>
           <t>Experto en implementación y soporte técnico de SAP Business One.
 Configura y administra la plataforma a nivel técnico.
-Desarrolla personalizaciones, integraciones y extensiones.
-Optimiza el rendimiento y la operación del sistema.</t>
+Desarrolla personalizaciones, integraciones y extensiones.</t>
         </is>
       </c>
     </row>
@@ -3848,8 +3810,7 @@
         <is>
           <t>Experto en implementación funcional de SAP Business One.
 Configura procesos empresariales y flujos operativos.
-Acompaña al usuario en la adopción de la solución.
-Optimiza la gestión y operación del negocio.</t>
+Acompaña al usuario en la adopción de la solución.</t>
         </is>
       </c>
     </row>
@@ -3865,8 +3826,7 @@
         <is>
           <t>Experto en soluciones SAP enfocadas en experiencia del cliente.
 Optimiza procesos comerciales y de atención al cliente.
-Configura e integra módulos de SAP CX.
-Mejora la relación y fidelización de clientes.</t>
+Configura e integra módulos de SAP CX.</t>
         </is>
       </c>
     </row>
@@ -4017,8 +3977,7 @@
         <is>
           <t>Experto en desarrollo de aplicaciones móviles multiplataforma.
 Construye soluciones para iOS y Android con Flutter y React Native.
-Integra servicios backend, APIs y bases de datos.
-Optimiza rendimiento y experiencia de usuario.</t>
+Integra servicios backend, APIs y bases de datos.</t>
         </is>
       </c>
     </row>
@@ -4034,8 +3993,7 @@
         <is>
           <t>Experto en desarrollo de aplicaciones móviles multiplataforma.
 Implementa soluciones móviles usando Flutter e Ionic.
-Integra funcionalidades, servicios y APIs.
-Garantiza aplicaciones eficientes y mantenibles.</t>
+Integra funcionalidades, servicios y APIs.</t>
         </is>
       </c>
     </row>
@@ -4075,9 +4033,7 @@
       <c r="D84" s="8" t="inlineStr">
         <is>
           <t>Experto en asesoría y acompañamiento técnico en proyectos de desarrollo.
-Analiza requerimientos y propone soluciones tecnológicas adecuadas.
-Apoya la toma de decisiones técnicas y funcionales.
-Optimiza procesos y calidad del desarrollo.</t>
+Analiza requerimientos y propone soluciones tecnológicas adecuadas.</t>
         </is>
       </c>
     </row>
@@ -4093,8 +4049,7 @@
         <is>
           <t>Experto en levantamiento y análisis de requerimientos del negocio.
 Traduce necesidades funcionales en especificaciones claras.
-Actúa como enlace entre usuarios y equipo técnico.
-Asegura alineación de la solución con los objetivos del negocio.</t>
+Actúa como enlace entre usuarios y equipo técnico.</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4063,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Desarrollador Liferay especializado en migraciones es un profesional con habilidades técnicas avanzadas en la plataforma Liferay DXP (Digital Experience Platform), enfocado en modernizar, optimizar y trasladar portales empresariales heredados a arquitecturas más actualizadas, garantizando continuidad operativa, seguridad y escalabilidad.</t>
+          <t>Desarrollador Liferay especializado en migraciones es un profesional con habilidades técnicas avanzadas en la plataforma Liferay DXP (Digital Experience Platform), enfocado en modernizar, op</t>
         </is>
       </c>
     </row>
@@ -4124,8 +4079,7 @@
         <is>
           <t>Experto en análisis y desarrollo de soluciones tecnológicas.
 Combina visión funcional con implementación técnica.
-Desarrolla y ajusta aplicaciones según requerimientos.
-Optimiza procesos y funcionalidades del sistema.</t>
+Desarrolla y ajusta aplicaciones según requerimientos.</t>
         </is>
       </c>
     </row>

--- a/periferia_v2/data/Generales_para_todos.xlsx
+++ b/periferia_v2/data/Generales_para_todos.xlsx
@@ -2534,14 +2534,14 @@
     <mergeCell ref="A39:A49"/>
     <mergeCell ref="A50:A62"/>
     <mergeCell ref="A15:A25"/>
-    <mergeCell ref="A146:A159"/>
     <mergeCell ref="A91:A98"/>
     <mergeCell ref="A99:A113"/>
     <mergeCell ref="A77:A90"/>
     <mergeCell ref="A135:A145"/>
+    <mergeCell ref="A160:A167"/>
     <mergeCell ref="A2:A14"/>
-    <mergeCell ref="A160:A167"/>
     <mergeCell ref="A63:A76"/>
+    <mergeCell ref="A146:A159"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4063,7 +4063,9 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Desarrollador Liferay especializado en migraciones es un profesional con habilidades técnicas avanzadas en la plataforma Liferay DXP (Digital Experience Platform), enfocado en modernizar, op</t>
+          <t>Especialista en la plataforma Liferay DXP.
+Implementa y migra portales empresariales a arquitecturas modernas.
+Garantiza continuidad operativa, seguridad y escalabilidad.</t>
         </is>
       </c>
     </row>
